--- a/0-MBA/A Study on Adoption of AI Techniques for Demand Forecasting among Textile Manufacturing Units in Tiruppur, Tamil Nadu (Responses) (1).xlsx
+++ b/0-MBA/A Study on Adoption of AI Techniques for Demand Forecasting among Textile Manufacturing Units in Tiruppur, Tamil Nadu (Responses) (1).xlsx
@@ -1,18 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="130" yWindow="490" windowWidth="18880" windowHeight="8740"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="DESCRIPTIVE_ANALYSIS" sheetId="2" r:id="rId6"/>
+    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
+    <sheet name="DESCRIPTIVE_ANALYSIS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="263">
   <si>
     <t>Timestamp</t>
   </si>
@@ -783,38 +786,66 @@
   </si>
   <si>
     <t>vinupriya85197@gmail.com</t>
+  </si>
+  <si>
+    <t>maazamango95795@gmail.com</t>
+  </si>
+  <si>
+    <t>backup109898@gmail.com</t>
+  </si>
+  <si>
+    <t>bbird7172@gmail.com</t>
+  </si>
+  <si>
+    <t>akshsm25@gmail.com</t>
+  </si>
+  <si>
+    <t>nandhana.m963@gmail.com</t>
+  </si>
+  <si>
+    <t>ashwathielango@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -828,9 +859,27 @@
         <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
-    <border/>
+  <borders count="15">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
@@ -844,6 +893,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -858,6 +908,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -872,93 +923,250 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -975,24 +1183,45 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Form Responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,52 +1229,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AK69" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:AK76">
   <tableColumns count="37">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="1. Is your current workplace located in Tiruppur, Tamil Nadu?" id="2"/>
-    <tableColumn name="2. What is your current designation?" id="3"/>
-    <tableColumn name="3. How many years of experience do you have in the textile industry?" id="4"/>
-    <tableColumn name="4. What is the primary activity of your organization?" id="5"/>
-    <tableColumn name="5. What is the approximate size of your organization?" id="6"/>
-    <tableColumn name="6. Does your organization currently use demand forecasting for production planning?" id="7"/>
-    <tableColumn name="7. What is the primary method used for demand forecasting in your organization?" id="8"/>
-    <tableColumn name="8. How frequently is demand forecasting performed?" id="9"/>
-    <tableColumn name="9. Which information is primarily used for demand forecasting?" id="10"/>
-    <tableColumn name="10. Which factor has the greatest influence on demand variation in your organization?" id="11"/>
-    <tableColumn name="11. How would you describe the effectiveness of the current demand forecasting process?" id="12"/>
-    <tableColumn name="12. How would you describe your awareness of Artificial Intelligence applications in business?" id="13"/>
-    <tableColumn name="13. How familiar are you with the use of AI / Machine Learning for demand forecasting?" id="14"/>
-    <tableColumn name="14. Which AI / analytics application are you most familiar with?" id="15"/>
-    <tableColumn name="15. Through which source have you mainly learned about AI applications?" id="16"/>
-    <tableColumn name="16. Which statement best describes your organization's current level of AI adoption?" id="17"/>
-    <tableColumn name="17. In which business area is AI / analytics currently being used or planned to be used?" id="18"/>
-    <tableColumn name="18. What is the current level of AI / analytics usage in your organization?" id="19"/>
-    <tableColumn name="19. Which AI / ML technique is your organization most familiar with or currently considering for business applications?" id="20"/>
-    <tableColumn name="20. What is the current level of technological infrastructure available for AI / analytics?" id="21"/>
-    <tableColumn name="21. How would you describe the availability of historical data required for AI-based demand forecasting?" id="22"/>
-    <tableColumn name="22. How would you describe the availability of employees with AI / analytics skills?" id="23"/>
-    <tableColumn name="23. How prepared is your organization to adopt AI-based demand forecasting?" id="24"/>
-    <tableColumn name="24. What is the current level of management support for AI adoption?" id="25"/>
-    <tableColumn name="25. What level of investment would your organization be willing to make for AI-based demand forecasting?" id="26"/>
-    <tableColumn name="26. How likely is your organization to adopt AI-based demand forecasting within the next three years?" id="27"/>
-    <tableColumn name="27. Which area would benefit the most from AI-based demand forecasting?" id="28"/>
-    <tableColumn name="28. What level of improvement in forecasting accuracy would you expect from AI-based forecasting?" id="29"/>
-    <tableColumn name="29. What impact would AI-based demand forecasting have on inventory management?" id="30"/>
-    <tableColumn name="30. What impact would AI-based demand forecasting have on managerial decision-making?" id="31"/>
-    <tableColumn name="31. What would be the biggest challenge for your organization in adopting AI-based demand forecasting?" id="32"/>
-    <tableColumn name="32. Which factor should receive the highest priority to improve AI adoption for demand forecasting?" id="33"/>
-    <tableColumn name="33. Which approach would be most suitable for introducing AI-based demand forecasting in your organization?" id="34"/>
-    <tableColumn name="Name or Email Address:" id="35"/>
-    <tableColumn name="Email Address" id="36"/>
-    <tableColumn name="Column 34" id="37"/>
+    <tableColumn id="1" name="Timestamp"/>
+    <tableColumn id="2" name="1. Is your current workplace located in Tiruppur, Tamil Nadu?"/>
+    <tableColumn id="3" name="2. What is your current designation?"/>
+    <tableColumn id="4" name="3. How many years of experience do you have in the textile industry?"/>
+    <tableColumn id="5" name="4. What is the primary activity of your organization?"/>
+    <tableColumn id="6" name="5. What is the approximate size of your organization?"/>
+    <tableColumn id="7" name="6. Does your organization currently use demand forecasting for production planning?"/>
+    <tableColumn id="8" name="7. What is the primary method used for demand forecasting in your organization?"/>
+    <tableColumn id="9" name="8. How frequently is demand forecasting performed?"/>
+    <tableColumn id="10" name="9. Which information is primarily used for demand forecasting?"/>
+    <tableColumn id="11" name="10. Which factor has the greatest influence on demand variation in your organization?"/>
+    <tableColumn id="12" name="11. How would you describe the effectiveness of the current demand forecasting process?"/>
+    <tableColumn id="13" name="12. How would you describe your awareness of Artificial Intelligence applications in business?"/>
+    <tableColumn id="14" name="13. How familiar are you with the use of AI / Machine Learning for demand forecasting?"/>
+    <tableColumn id="15" name="14. Which AI / analytics application are you most familiar with?"/>
+    <tableColumn id="16" name="15. Through which source have you mainly learned about AI applications?"/>
+    <tableColumn id="17" name="16. Which statement best describes your organization's current level of AI adoption?"/>
+    <tableColumn id="18" name="17. In which business area is AI / analytics currently being used or planned to be used?"/>
+    <tableColumn id="19" name="18. What is the current level of AI / analytics usage in your organization?"/>
+    <tableColumn id="20" name="19. Which AI / ML technique is your organization most familiar with or currently considering for business applications?"/>
+    <tableColumn id="21" name="20. What is the current level of technological infrastructure available for AI / analytics?"/>
+    <tableColumn id="22" name="21. How would you describe the availability of historical data required for AI-based demand forecasting?"/>
+    <tableColumn id="23" name="22. How would you describe the availability of employees with AI / analytics skills?"/>
+    <tableColumn id="24" name="23. How prepared is your organization to adopt AI-based demand forecasting?"/>
+    <tableColumn id="25" name="24. What is the current level of management support for AI adoption?"/>
+    <tableColumn id="26" name="25. What level of investment would your organization be willing to make for AI-based demand forecasting?"/>
+    <tableColumn id="27" name="26. How likely is your organization to adopt AI-based demand forecasting within the next three years?"/>
+    <tableColumn id="28" name="27. Which area would benefit the most from AI-based demand forecasting?"/>
+    <tableColumn id="29" name="28. What level of improvement in forecasting accuracy would you expect from AI-based forecasting?"/>
+    <tableColumn id="30" name="29. What impact would AI-based demand forecasting have on inventory management?"/>
+    <tableColumn id="31" name="30. What impact would AI-based demand forecasting have on managerial decision-making?"/>
+    <tableColumn id="32" name="31. What would be the biggest challenge for your organization in adopting AI-based demand forecasting?"/>
+    <tableColumn id="33" name="32. Which factor should receive the highest priority to improve AI adoption for demand forecasting?"/>
+    <tableColumn id="34" name="33. Which approach would be most suitable for introducing AI-based demand forecasting in your organization?"/>
+    <tableColumn id="35" name="Name or Email Address:"/>
+    <tableColumn id="36" name="Email Address"/>
+    <tableColumn id="37" name="Column 34"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1235,24 +1464,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AK76"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.88"/>
-    <col customWidth="1" min="2" max="2" width="37.63"/>
-    <col customWidth="1" min="3" max="3" width="31.25"/>
-    <col customWidth="1" min="4" max="34" width="37.63"/>
-    <col customWidth="1" min="35" max="43" width="18.88"/>
+    <col min="1" max="1" width="18.90625" customWidth="1"/>
+    <col min="2" max="2" width="37.6328125" customWidth="1"/>
+    <col min="3" max="3" width="31.26953125" customWidth="1"/>
+    <col min="4" max="34" width="37.6328125" customWidth="1"/>
+    <col min="35" max="43" width="18.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:37" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1597,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:37" ht="22.5" customHeight="1">
       <c r="A2" s="3">
         <v>46260.464479155096</v>
       </c>
@@ -1476,9 +1708,9 @@
       </c>
       <c r="AK2" s="5"/>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:37" ht="22.5" customHeight="1">
       <c r="A3" s="3">
-        <v>46260.46894373842</v>
+        <v>46260.468943738422</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>37</v>
@@ -1587,9 +1819,9 @@
       </c>
       <c r="AK3" s="5"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:37" ht="22.5" customHeight="1">
       <c r="A4" s="6">
-        <v>46260.47118263889</v>
+        <v>46260.471182638888</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>37</v>
@@ -1698,9 +1930,9 @@
       </c>
       <c r="AK4" s="8"/>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:37" ht="22.5" customHeight="1">
       <c r="A5" s="6">
-        <v>46260.47133864583</v>
+        <v>46260.471338645832</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>37</v>
@@ -1809,7 +2041,7 @@
       </c>
       <c r="AK5" s="8"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:37" ht="22.5" customHeight="1">
       <c r="A6" s="6">
         <v>46260.476622939816</v>
       </c>
@@ -1919,9 +2151,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:37" ht="22.5" customHeight="1">
       <c r="A7" s="6">
-        <v>46260.47671461805</v>
+        <v>46260.476714618053</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>37</v>
@@ -2029,9 +2261,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:37" ht="22.5" customHeight="1">
       <c r="A8" s="6">
-        <v>46260.47673954861</v>
+        <v>46260.476739548612</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>37</v>
@@ -2139,9 +2371,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:37" ht="22.5" customHeight="1">
       <c r="A9" s="6">
-        <v>46260.47763393518</v>
+        <v>46260.477633935181</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>37</v>
@@ -2249,7 +2481,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:37" ht="22.5" customHeight="1">
       <c r="A10" s="6">
         <v>46260.478458171296</v>
       </c>
@@ -2359,7 +2591,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:37" ht="22.5" customHeight="1">
       <c r="A11" s="6">
         <v>46260.484495717596</v>
       </c>
@@ -2469,7 +2701,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:37" ht="22.5" customHeight="1">
       <c r="A12" s="6">
         <v>46260.486437997686</v>
       </c>
@@ -2579,7 +2811,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:37" ht="22.5" customHeight="1">
       <c r="A13" s="6">
         <v>46260.487235532404</v>
       </c>
@@ -2689,7 +2921,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:37" ht="22.5" customHeight="1">
       <c r="A14" s="6">
         <v>46260.489387152775</v>
       </c>
@@ -2799,9 +3031,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:37" ht="22.5" customHeight="1">
       <c r="A15" s="6">
-        <v>46260.49136395833</v>
+        <v>46260.491363958332</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>37</v>
@@ -2909,7 +3141,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:37" ht="22.5" customHeight="1">
       <c r="A16" s="6">
         <v>46260.497829189815</v>
       </c>
@@ -3019,9 +3251,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:36" ht="22.5" customHeight="1">
       <c r="A17" s="6">
-        <v>46260.49899965277</v>
+        <v>46260.498999652773</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>37</v>
@@ -3129,7 +3361,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" spans="1:36" ht="22.5" customHeight="1">
       <c r="A18" s="6">
         <v>46260.515472604166</v>
       </c>
@@ -3239,9 +3471,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:36" ht="22.5" customHeight="1">
       <c r="A19" s="6">
-        <v>46260.53176883102</v>
+        <v>46260.531768831017</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>37</v>
@@ -3349,9 +3581,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" spans="1:36" ht="22.5" customHeight="1">
       <c r="A20" s="6">
-        <v>46260.53382814815</v>
+        <v>46260.533828148153</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>37</v>
@@ -3459,9 +3691,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" spans="1:36" ht="22.5" customHeight="1">
       <c r="A21" s="6">
-        <v>46260.54117203703</v>
+        <v>46260.541172037032</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>37</v>
@@ -3569,7 +3801,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
+    <row r="22" spans="1:36" ht="22.5" customHeight="1">
       <c r="A22" s="6">
         <v>46260.678269571756</v>
       </c>
@@ -3679,7 +3911,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" spans="1:36" ht="22.5" customHeight="1">
       <c r="A23" s="6">
         <v>46260.725811145836</v>
       </c>
@@ -3789,9 +4021,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" spans="1:36" ht="22.5" customHeight="1">
       <c r="A24" s="6">
-        <v>46260.78314799769</v>
+        <v>46260.783147997689</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>37</v>
@@ -3899,9 +4131,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" spans="1:36" ht="22.5" customHeight="1">
       <c r="A25" s="6">
-        <v>46260.78691684028</v>
+        <v>46260.786916840283</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>37</v>
@@ -4009,9 +4241,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
+    <row r="26" spans="1:36" ht="22.5" customHeight="1">
       <c r="A26" s="6">
-        <v>46261.4413530787</v>
+        <v>46261.441353078699</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>37</v>
@@ -4119,9 +4351,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:36" ht="22.5" customHeight="1">
       <c r="A27" s="6">
-        <v>46261.45912383102</v>
+        <v>46261.459123831017</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>37</v>
@@ -4229,7 +4461,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" spans="1:36" ht="22.5" customHeight="1">
       <c r="A28" s="6">
         <v>46261.489001608796</v>
       </c>
@@ -4339,9 +4571,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
+    <row r="29" spans="1:36" ht="22.5" customHeight="1">
       <c r="A29" s="6">
-        <v>46261.48919392361</v>
+        <v>46261.489193923611</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>37</v>
@@ -4449,7 +4681,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
+    <row r="30" spans="1:36" ht="22.5" customHeight="1">
       <c r="A30" s="6">
         <v>46261.492357615745</v>
       </c>
@@ -4559,9 +4791,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
+    <row r="31" spans="1:36" ht="22.5" customHeight="1">
       <c r="A31" s="6">
-        <v>46261.52185197917</v>
+        <v>46261.521851979167</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>37</v>
@@ -4669,7 +4901,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
+    <row r="32" spans="1:36" ht="22.5" customHeight="1">
       <c r="A32" s="6">
         <v>46261.627236562505</v>
       </c>
@@ -4779,9 +5011,9 @@
         <v>215</v>
       </c>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
+    <row r="33" spans="1:36" ht="22.5" customHeight="1">
       <c r="A33" s="6">
-        <v>46261.63080321759</v>
+        <v>46261.630803217588</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>37</v>
@@ -4889,7 +5121,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
+    <row r="34" spans="1:36" ht="22.5" customHeight="1">
       <c r="A34" s="6">
         <v>46261.651500266205</v>
       </c>
@@ -4999,9 +5231,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
+    <row r="35" spans="1:36" ht="22.5" customHeight="1">
       <c r="A35" s="6">
-        <v>46261.74069357639</v>
+        <v>46261.740693576387</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>37</v>
@@ -5109,9 +5341,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="36" ht="22.5" customHeight="1">
+    <row r="36" spans="1:36" ht="22.5" customHeight="1">
       <c r="A36" s="6">
-        <v>46265.52728922454</v>
+        <v>46265.527289224541</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>37</v>
@@ -5219,9 +5451,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
+    <row r="37" spans="1:36" ht="22.5" customHeight="1">
       <c r="A37" s="6">
-        <v>46265.52889677083</v>
+        <v>46265.528896770833</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>37</v>
@@ -5329,7 +5561,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" ht="22.5" customHeight="1">
+    <row r="38" spans="1:36" ht="22.5" customHeight="1">
       <c r="A38" s="6">
         <v>46265.53034513889</v>
       </c>
@@ -5439,9 +5671,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
+    <row r="39" spans="1:36" ht="22.5" customHeight="1">
       <c r="A39" s="6">
-        <v>46265.53188460648</v>
+        <v>46265.531884606477</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>37</v>
@@ -5549,9 +5781,9 @@
         <v>222</v>
       </c>
     </row>
-    <row r="40" ht="22.5" customHeight="1">
+    <row r="40" spans="1:36" ht="22.5" customHeight="1">
       <c r="A40" s="6">
-        <v>46265.5335134375</v>
+        <v>46265.533513437498</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>37</v>
@@ -5659,9 +5891,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
+    <row r="41" spans="1:36" ht="22.5" customHeight="1">
       <c r="A41" s="6">
-        <v>46265.5347303125</v>
+        <v>46265.534730312502</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>37</v>
@@ -5769,7 +6001,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
+    <row r="42" spans="1:36" ht="22.5" customHeight="1">
       <c r="A42" s="6">
         <v>46265.53576506945</v>
       </c>
@@ -5879,9 +6111,9 @@
         <v>226</v>
       </c>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
+    <row r="43" spans="1:36" ht="22.5" customHeight="1">
       <c r="A43" s="6">
-        <v>46265.53713631944</v>
+        <v>46265.537136319443</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>37</v>
@@ -5989,7 +6221,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" ht="22.5" customHeight="1">
+    <row r="44" spans="1:36" ht="22.5" customHeight="1">
       <c r="A44" s="6">
         <v>46270.649022060185</v>
       </c>
@@ -6099,7 +6331,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" ht="22.5" customHeight="1">
+    <row r="45" spans="1:36" ht="22.5" customHeight="1">
       <c r="A45" s="6">
         <v>46270.651399560185</v>
       </c>
@@ -6209,9 +6441,9 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
+    <row r="46" spans="1:36" ht="22.5" customHeight="1">
       <c r="A46" s="6">
-        <v>46270.65306491898</v>
+        <v>46270.653064918981</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>37</v>
@@ -6319,9 +6551,9 @@
         <v>232</v>
       </c>
     </row>
-    <row r="47" ht="22.5" customHeight="1">
+    <row r="47" spans="1:36" ht="22.5" customHeight="1">
       <c r="A47" s="6">
-        <v>46270.67282475694</v>
+        <v>46270.672824756941</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>37</v>
@@ -6429,7 +6661,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" ht="22.5" customHeight="1">
+    <row r="48" spans="1:36" ht="22.5" customHeight="1">
       <c r="A48" s="6">
         <v>46270.67743708333</v>
       </c>
@@ -6539,9 +6771,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
+    <row r="49" spans="1:36" ht="22.5" customHeight="1">
       <c r="A49" s="6">
-        <v>46270.68028534722</v>
+        <v>46270.680285347218</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>37</v>
@@ -6649,9 +6881,9 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" ht="22.5" customHeight="1">
+    <row r="50" spans="1:36" ht="22.5" customHeight="1">
       <c r="A50" s="6">
-        <v>46270.68261421296</v>
+        <v>46270.682614212958</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>37</v>
@@ -6759,7 +6991,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" ht="22.5" customHeight="1">
+    <row r="51" spans="1:36" ht="22.5" customHeight="1">
       <c r="A51" s="6">
         <v>46270.686897974534</v>
       </c>
@@ -6869,7 +7101,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
+    <row r="52" spans="1:36" ht="22.5" customHeight="1">
       <c r="A52" s="6">
         <v>46270.696926516204</v>
       </c>
@@ -6979,9 +7211,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" ht="22.5" customHeight="1">
+    <row r="53" spans="1:36" ht="22.5" customHeight="1">
       <c r="A53" s="6">
-        <v>46270.7026225</v>
+        <v>46270.702622500001</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>37</v>
@@ -7089,9 +7321,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" ht="22.5" customHeight="1">
+    <row r="54" spans="1:36" ht="22.5" customHeight="1">
       <c r="A54" s="6">
-        <v>46270.70446412037</v>
+        <v>46270.704464120368</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>37</v>
@@ -7199,9 +7431,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" ht="22.5" customHeight="1">
+    <row r="55" spans="1:36" ht="22.5" customHeight="1">
       <c r="A55" s="6">
-        <v>46270.70581990741</v>
+        <v>46270.705819907409</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>37</v>
@@ -7309,7 +7541,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
+    <row r="56" spans="1:36" ht="22.5" customHeight="1">
       <c r="A56" s="6">
         <v>46270.70705636574</v>
       </c>
@@ -7419,9 +7651,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" ht="22.5" customHeight="1">
+    <row r="57" spans="1:36" ht="22.5" customHeight="1">
       <c r="A57" s="6">
-        <v>46272.83208677083</v>
+        <v>46272.832086770832</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>37</v>
@@ -7529,7 +7761,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="58" ht="22.5" customHeight="1">
+    <row r="58" spans="1:36" ht="22.5" customHeight="1">
       <c r="A58" s="6">
         <v>46272.839747210644</v>
       </c>
@@ -7639,9 +7871,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="59" ht="22.5" customHeight="1">
+    <row r="59" spans="1:36" ht="22.5" customHeight="1">
       <c r="A59" s="6">
-        <v>46272.88716921296</v>
+        <v>46272.887169212961</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>37</v>
@@ -7749,9 +7981,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="60" ht="22.5" customHeight="1">
+    <row r="60" spans="1:36" ht="22.5" customHeight="1">
       <c r="A60" s="6">
-        <v>46273.29875689815</v>
+        <v>46273.298756898148</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>37</v>
@@ -7859,7 +8091,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="61" ht="22.5" customHeight="1">
+    <row r="61" spans="1:36" ht="22.5" customHeight="1">
       <c r="A61" s="6">
         <v>46273.439103067125</v>
       </c>
@@ -7969,9 +8201,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="62" ht="22.5" customHeight="1">
+    <row r="62" spans="1:36" ht="22.5" customHeight="1">
       <c r="A62" s="6">
-        <v>46275.81144839121</v>
+        <v>46275.811448391207</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>37</v>
@@ -8079,7 +8311,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="63" ht="22.5" customHeight="1">
+    <row r="63" spans="1:36" ht="22.5" customHeight="1">
       <c r="A63" s="6">
         <v>46275.878587071755</v>
       </c>
@@ -8189,9 +8421,9 @@
         <v>250</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1">
+    <row r="64" spans="1:36" ht="22.5" customHeight="1">
       <c r="A64" s="6">
-        <v>46276.30281003472</v>
+        <v>46276.302810034722</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>37</v>
@@ -8299,9 +8531,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="65" ht="22.5" customHeight="1">
+    <row r="65" spans="1:37" ht="22.5" customHeight="1">
       <c r="A65" s="6">
-        <v>46276.30547872685</v>
+        <v>46276.305478726848</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>37</v>
@@ -8409,7 +8641,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" ht="22.5" customHeight="1">
+    <row r="66" spans="1:37" ht="22.5" customHeight="1">
       <c r="A66" s="6">
         <v>46278.285181643514</v>
       </c>
@@ -8519,7 +8751,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="67" ht="22.5" customHeight="1">
+    <row r="67" spans="1:37" ht="22.5" customHeight="1">
       <c r="A67" s="6">
         <v>46278.286424328704</v>
       </c>
@@ -8629,7 +8861,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" ht="22.5" customHeight="1">
+    <row r="68" spans="1:37" ht="22.5" customHeight="1">
       <c r="A68" s="6">
         <v>46278.320172395834</v>
       </c>
@@ -8739,7 +8971,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="69" ht="22.5" customHeight="1">
+    <row r="69" spans="1:37" ht="22.5" customHeight="1" thickBot="1">
       <c r="A69" s="6">
         <v>46278.325313877314</v>
       </c>
@@ -8849,21 +9081,799 @@
         <v>256</v>
       </c>
     </row>
+    <row r="70" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A70" s="13">
+        <v>46280.448553240742</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="N70" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O70" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="P70" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q70" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="R70" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="S70" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="T70" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="U70" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="V70" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="W70" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="X70" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y70" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z70" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA70" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB70" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC70" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD70" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE70" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF70" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG70" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH70" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI70" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ70" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AK70" s="15"/>
+    </row>
+    <row r="71" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A71" s="16">
+        <v>46280.44972222222</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H71" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J71" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L71" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="M71" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="O71" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="P71" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q71" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="R71" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="S71" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="T71" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="U71" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="V71" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="W71" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="X71" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y71" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z71" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA71" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB71" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC71" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD71" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE71" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF71" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG71" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="AH71" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI71" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ71" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK71" s="18"/>
+    </row>
+    <row r="72" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A72" s="19">
+        <v>46280.450787037036</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="I72" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="K72" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="N72" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="O72" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P72" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q72" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="R72" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="S72" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="T72" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="U72" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="V72" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="W72" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="X72" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y72" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z72" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA72" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB72" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC72" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD72" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE72" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF72" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG72" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH72" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI72" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ72" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK72" s="21"/>
+    </row>
+    <row r="73" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A73" s="16">
+        <v>46280.451655092591</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G73" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H73" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J73" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L73" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="M73" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="O73" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="P73" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q73" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="R73" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="S73" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="T73" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="U73" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="V73" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="W73" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="X73" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y73" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z73" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA73" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB73" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC73" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD73" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE73" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF73" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG73" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH73" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI73" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="AJ73" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK73" s="18"/>
+    </row>
+    <row r="74" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A74" s="19">
+        <v>46280.462037037039</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="L74" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="N74" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="P74" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q74" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="R74" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="S74" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="T74" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="U74" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="V74" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="W74" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="X74" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y74" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z74" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA74" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB74" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC74" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD74" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE74" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF74" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG74" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="AH74" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI74" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="AJ74" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="AK74" s="21"/>
+    </row>
+    <row r="75" spans="1:37" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A75" s="16">
+        <v>46281.363888888889</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G75" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I75" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J75" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="M75" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O75" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="P75" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q75" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="R75" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="S75" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="T75" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="U75" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="V75" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="W75" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="X75" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y75" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z75" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA75" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB75" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC75" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD75" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE75" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF75" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG75" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH75" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI75" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="AJ75" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK75" s="18"/>
+    </row>
+    <row r="76" spans="1:37" ht="15.75" customHeight="1">
+      <c r="A76" s="22">
+        <v>46281.364988425928</v>
+      </c>
+      <c r="B76" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I76" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="J76" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="K76" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="L76" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="N76" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="O76" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="P76" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q76" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="R76" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="S76" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="T76" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="U76" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="V76" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="W76" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="X76" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y76" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z76" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA76" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB76" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC76" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD76" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE76" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF76" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG76" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH76" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI76" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="AJ76" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK76" s="24"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>